--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_COLEGIO EL PINAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_COLEGIO EL PINAR.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>58.2293</v>
+        <v>63.7312</v>
       </c>
       <c r="E2" t="n">
-        <v>40.5231</v>
+        <v>33.102</v>
       </c>
       <c r="F2" t="n">
-        <v>17.7058</v>
+        <v>30.6293</v>
       </c>
       <c r="G2" t="n">
-        <v>34.4411</v>
+        <v>30.7022</v>
       </c>
       <c r="H2" t="n">
-        <v>31.6079</v>
+        <v>13.6232</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8334</v>
+        <v>17.079</v>
       </c>
       <c r="J2" t="n">
-        <v>52.8443</v>
+        <v>34.1256</v>
       </c>
       <c r="K2" t="n">
-        <v>43.9314</v>
+        <v>17.5931</v>
       </c>
       <c r="L2" t="n">
-        <v>8.912700000000001</v>
+        <v>16.5326</v>
       </c>
       <c r="M2" t="n">
-        <v>-18.4032</v>
+        <v>-3.4232</v>
       </c>
       <c r="N2" t="n">
-        <v>-12.3233</v>
+        <v>-3.9698</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.0793</v>
+        <v>0.5462999999999993</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.369700000000001</v>
+        <v>16.4524</v>
       </c>
       <c r="Q2" t="n">
-        <v>-51.7359</v>
+        <v>-20.4168</v>
       </c>
       <c r="R2" t="n">
-        <v>48.3665</v>
+        <v>36.8695</v>
       </c>
       <c r="S2" t="n">
-        <v>15.467</v>
+        <v>0.06750000000000028</v>
       </c>
       <c r="T2" t="n">
-        <v>5.943200000000001</v>
+        <v>-0.1715</v>
       </c>
       <c r="U2" t="n">
-        <v>9.5236</v>
+        <v>0.2395000000000003</v>
       </c>
       <c r="V2" t="n">
-        <v>11.6908</v>
+        <v>16.5091</v>
       </c>
       <c r="W2" t="n">
-        <v>33.4723</v>
+        <v>19.5653</v>
       </c>
       <c r="X2" t="n">
-        <v>-21.7812</v>
+        <v>-3.0559</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>56.5546</v>
+        <v>54.3876</v>
       </c>
       <c r="E3" t="n">
-        <v>27.8213</v>
+        <v>38.9689</v>
       </c>
       <c r="F3" t="n">
-        <v>28.733</v>
+        <v>15.419</v>
       </c>
       <c r="G3" t="n">
-        <v>30.7022</v>
+        <v>34.4411</v>
       </c>
       <c r="H3" t="n">
-        <v>13.6232</v>
+        <v>31.6079</v>
       </c>
       <c r="I3" t="n">
-        <v>17.079</v>
+        <v>2.8334</v>
       </c>
       <c r="J3" t="n">
-        <v>34.1256</v>
+        <v>52.8443</v>
       </c>
       <c r="K3" t="n">
-        <v>17.5931</v>
+        <v>43.9314</v>
       </c>
       <c r="L3" t="n">
-        <v>16.5326</v>
+        <v>8.912700000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4232</v>
+        <v>-18.4032</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.9698</v>
+        <v>-12.3233</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5462999999999993</v>
+        <v>-6.0793</v>
       </c>
       <c r="P3" t="n">
-        <v>16.4524</v>
+        <v>-3.369700000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-20.4168</v>
+        <v>-51.7359</v>
       </c>
       <c r="R3" t="n">
-        <v>36.8695</v>
+        <v>48.3665</v>
       </c>
       <c r="S3" t="n">
-        <v>-7.1092</v>
+        <v>11.6252</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.4523</v>
+        <v>4.3884</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.6568</v>
+        <v>7.2371</v>
       </c>
       <c r="V3" t="n">
-        <v>16.5091</v>
+        <v>11.6908</v>
       </c>
       <c r="W3" t="n">
-        <v>19.5653</v>
+        <v>33.4723</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.0559</v>
+        <v>-21.7812</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>42.5437</v>
+        <v>42.1323</v>
       </c>
       <c r="E4" t="n">
-        <v>17.0414</v>
+        <v>17.0211</v>
       </c>
       <c r="F4" t="n">
-        <v>25.5021</v>
+        <v>25.1112</v>
       </c>
       <c r="G4" t="n">
         <v>25.5369</v>
@@ -766,13 +766,13 @@
         <v>61.4491</v>
       </c>
       <c r="S4" t="n">
-        <v>11.7349</v>
+        <v>11.3237</v>
       </c>
       <c r="T4" t="n">
-        <v>8.0916</v>
+        <v>8.071300000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>3.6435</v>
+        <v>3.2523</v>
       </c>
       <c r="V4" t="n">
         <v>21.3275</v>
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>36.7883</v>
+        <v>22.9197</v>
       </c>
       <c r="E5" t="n">
-        <v>43.6468</v>
+        <v>26.9363</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.8588</v>
+        <v>-4.0169</v>
       </c>
       <c r="G5" t="n">
         <v>2.541100000000001</v>
@@ -844,13 +844,13 @@
         <v>47.7718</v>
       </c>
       <c r="S5" t="n">
-        <v>24.0481</v>
+        <v>10.1796</v>
       </c>
       <c r="T5" t="n">
-        <v>28.9454</v>
+        <v>12.2351</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.8973</v>
+        <v>-2.0555</v>
       </c>
       <c r="V5" t="n">
         <v>-9.2277</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>17.8067</v>
+        <v>21.6056</v>
       </c>
       <c r="E6" t="n">
-        <v>17.8067</v>
+        <v>9.910600000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>11.6948</v>
       </c>
       <c r="G6" t="n">
-        <v>17.8067</v>
+        <v>1.964400000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>6.356</v>
+        <v>-6.8794</v>
       </c>
       <c r="I6" t="n">
-        <v>11.4508</v>
+        <v>8.8438</v>
       </c>
       <c r="J6" t="n">
-        <v>17.8067</v>
+        <v>17.9235</v>
       </c>
       <c r="K6" t="n">
-        <v>6.356</v>
+        <v>2.461299999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>11.4508</v>
+        <v>15.462</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-15.959</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-9.3407</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-6.617999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>20.2188</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-17.0469</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>37.2658</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.727</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.003500000000000059</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.7305</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-3.3045</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>9.0383</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-12.3426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MUÑOZ LEIVA</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,31 +955,31 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>8.4457</v>
+        <v>17.8067</v>
       </c>
       <c r="E7" t="n">
-        <v>8.4457</v>
+        <v>17.8067</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4457</v>
+        <v>17.8067</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8162</v>
+        <v>6.356</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6295</v>
+        <v>11.4508</v>
       </c>
       <c r="J7" t="n">
-        <v>8.4457</v>
+        <v>17.8067</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8162</v>
+        <v>6.356</v>
       </c>
       <c r="L7" t="n">
-        <v>6.6295</v>
+        <v>11.4508</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. MUÑOZ LEIVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>8.4336</v>
+        <v>8.4457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03659999999999952</v>
+        <v>8.4457</v>
       </c>
       <c r="F8" t="n">
-        <v>8.3973</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.950799999999999</v>
+        <v>8.4457</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1162999999999994</v>
+        <v>1.8162</v>
       </c>
       <c r="I8" t="n">
-        <v>5.066800000000001</v>
+        <v>6.6295</v>
       </c>
       <c r="J8" t="n">
-        <v>6.7363</v>
+        <v>8.4457</v>
       </c>
       <c r="K8" t="n">
-        <v>3.0126</v>
+        <v>1.8162</v>
       </c>
       <c r="L8" t="n">
-        <v>3.7237</v>
+        <v>6.6295</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.785500000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.1291</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3436</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.162699999999999</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-24.5794</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>28.7423</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>18.0457</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>15.6769</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3686</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-18.7255</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2031</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.9284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>8.3779</v>
+        <v>8.020800000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.237000000000001</v>
+        <v>-3.8567</v>
       </c>
       <c r="F9" t="n">
-        <v>8.141</v>
+        <v>11.8777</v>
       </c>
       <c r="G9" t="n">
-        <v>1.964400000000001</v>
+        <v>0.5621000000000007</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.8794</v>
+        <v>-3.4826</v>
       </c>
       <c r="I9" t="n">
-        <v>8.8438</v>
+        <v>4.0448</v>
       </c>
       <c r="J9" t="n">
-        <v>17.9235</v>
+        <v>9.432499999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>2.461299999999999</v>
+        <v>4.2015</v>
       </c>
       <c r="L9" t="n">
-        <v>15.462</v>
+        <v>5.230799999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.959</v>
+        <v>-8.8704</v>
       </c>
       <c r="N9" t="n">
-        <v>-9.3407</v>
+        <v>-7.6841</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.617999999999999</v>
+        <v>-1.1861</v>
       </c>
       <c r="P9" t="n">
-        <v>20.2188</v>
+        <v>6.9378</v>
       </c>
       <c r="Q9" t="n">
-        <v>-17.0469</v>
+        <v>-20.4169</v>
       </c>
       <c r="R9" t="n">
-        <v>37.2658</v>
+        <v>27.3545</v>
       </c>
       <c r="S9" t="n">
-        <v>-10.5008</v>
+        <v>0.41</v>
       </c>
       <c r="T9" t="n">
-        <v>-9.6775</v>
+        <v>0.2373</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8231999999999999</v>
+        <v>0.1728000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.3045</v>
+        <v>0.1107</v>
       </c>
       <c r="W9" t="n">
-        <v>9.0383</v>
+        <v>6.8904</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.3426</v>
+        <v>-6.7798</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>5.296600000000002</v>
+        <v>7.3297</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.792099999999999</v>
+        <v>-5.569100000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>8.088999999999999</v>
+        <v>12.8989</v>
       </c>
       <c r="G10" t="n">
-        <v>1.416399999999999</v>
+        <v>-11.2358</v>
       </c>
       <c r="H10" t="n">
-        <v>6.21</v>
+        <v>-10.5544</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.7936</v>
+        <v>-0.6815000000000004</v>
       </c>
       <c r="J10" t="n">
-        <v>13.5905</v>
+        <v>-1.018</v>
       </c>
       <c r="K10" t="n">
-        <v>12.9154</v>
+        <v>-3.390000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6754000000000009</v>
+        <v>2.3722</v>
       </c>
       <c r="M10" t="n">
-        <v>-12.1737</v>
+        <v>-10.2179</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.705</v>
+        <v>-7.1643</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.469</v>
+        <v>-3.0533</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5769</v>
+        <v>6.541399999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-39.8426</v>
+        <v>-25.7688</v>
       </c>
       <c r="R10" t="n">
-        <v>37.2659</v>
+        <v>32.3106</v>
       </c>
       <c r="S10" t="n">
-        <v>4.302200000000001</v>
+        <v>-1.3345</v>
       </c>
       <c r="T10" t="n">
-        <v>7.601699999999999</v>
+        <v>-0.8872999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.2994</v>
+        <v>-0.4473</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1549</v>
+        <v>13.3585</v>
       </c>
       <c r="W10" t="n">
-        <v>15.8585</v>
+        <v>22.1053</v>
       </c>
       <c r="X10" t="n">
-        <v>-13.7039</v>
+        <v>-8.7468</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. RAGA RODRÍGUEZ</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>5.1296</v>
+        <v>6.106999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1296</v>
+        <v>-3.7751</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>9.881899999999998</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1296</v>
+        <v>1.416399999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5134</v>
+        <v>6.21</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6162</v>
+        <v>-4.7936</v>
       </c>
       <c r="J11" t="n">
-        <v>5.1296</v>
+        <v>13.5905</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5134</v>
+        <v>12.9154</v>
       </c>
       <c r="L11" t="n">
-        <v>3.6162</v>
+        <v>0.6754000000000009</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-12.1737</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-6.705</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-5.469</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-39.8426</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>37.2659</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>5.1125</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>6.6187</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1.5063</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.1549</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>15.8585</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-13.7039</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MUÑOZ MENDOZA</t>
+          <t>R. RAGA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,34 +1342,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9188</v>
+        <v>5.1296</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9188</v>
+        <v>5.1296</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9188</v>
+        <v>5.1296</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3027</v>
+        <v>1.5134</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6161</v>
+        <v>3.6162</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9188</v>
+        <v>5.1296</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3027</v>
+        <v>1.5134</v>
       </c>
       <c r="L12" t="n">
-        <v>3.6161</v>
+        <v>3.6162</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. MUÑOZ MENDOZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>2.737700000000002</v>
+        <v>3.9188</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.2727</v>
+        <v>3.9188</v>
       </c>
       <c r="F13" t="n">
-        <v>11.0102</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5621000000000007</v>
+        <v>3.9188</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.4826</v>
+        <v>0.3027</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0448</v>
+        <v>3.6161</v>
       </c>
       <c r="J13" t="n">
-        <v>9.432499999999999</v>
+        <v>3.9188</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2015</v>
+        <v>0.3027</v>
       </c>
       <c r="L13" t="n">
-        <v>5.230799999999999</v>
+        <v>3.6161</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.8704</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.6841</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1861</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6.9378</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.4169</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>27.3545</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8727</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.1789</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6940999999999999</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8904</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.7798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. VIÑUELA URBANO</t>
+          <t>N. ALVAREZ ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2053</v>
+        <v>2.3027</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2053</v>
+        <v>2.9107</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0.6083999999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2053</v>
+        <v>1.5851</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.1988</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2053</v>
+        <v>0.3865000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2053</v>
+        <v>3.1655</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.8966</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2053</v>
+        <v>1.2688</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-1.5805</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.698</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.8824000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.3696</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.5857</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.9554</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.0949</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.331</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0.2360999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-3.7471</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-3.7471</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VINUELA URBANO</t>
+          <t>M. VIÑUELA URBANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0165</v>
+        <v>1.2053</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9416</v>
+        <v>1.2053</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07489999999999999</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5981</v>
+        <v>1.2053</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1614</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7595</v>
+        <v>1.2053</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1207</v>
+        <v>1.2053</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0804</v>
+        <v>1.2053</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4774</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2018</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6791</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5572</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5543</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. ALVAREZ ALVAREZ</t>
+          <t>M. VINUELA URBANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0114</v>
+        <v>0.6548</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4574</v>
+        <v>0.636</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.446</v>
+        <v>0.0188</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5851</v>
+        <v>0.5981</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1988</v>
+        <v>-0.1614</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3865000000000001</v>
+        <v>0.7595</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1655</v>
+        <v>0.1207</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8966</v>
+        <v>0.0404</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2688</v>
+        <v>0.0804</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5805</v>
+        <v>0.4774</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.698</v>
+        <v>-0.2018</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8824000000000001</v>
+        <v>0.6791</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3696</v>
+        <v>0.1982</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5857</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.9554</v>
+        <v>0.1982</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1964</v>
+        <v>0.1955</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8775999999999999</v>
+        <v>0.2487</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0739</v>
+        <v>-0.0533</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.7471</v>
+        <v>-0.337</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.7471</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>A. TERNERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07669999999999955</v>
+        <v>0.02139999999999997</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.19</v>
+        <v>-2.3197</v>
       </c>
       <c r="F17" t="n">
-        <v>12.2667</v>
+        <v>2.3411</v>
       </c>
       <c r="G17" t="n">
-        <v>-8.9451</v>
+        <v>1.5803</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5291</v>
+        <v>0.8514</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.4743</v>
+        <v>0.7289</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.6474</v>
+        <v>0.4142</v>
       </c>
       <c r="K17" t="n">
-        <v>8.334199999999999</v>
+        <v>0.3701</v>
       </c>
       <c r="L17" t="n">
-        <v>-13.9818</v>
+        <v>0.0441</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2974</v>
+        <v>1.1661</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.8052</v>
+        <v>0.4813000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5075</v>
+        <v>0.6849</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3877</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-25.5703</v>
+        <v>-2.1804</v>
       </c>
       <c r="R17" t="n">
-        <v>24.1832</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>14.8505</v>
+        <v>-0.3607</v>
       </c>
       <c r="T17" t="n">
-        <v>11.3381</v>
+        <v>-0.2165</v>
       </c>
       <c r="U17" t="n">
-        <v>3.5127</v>
+        <v>-0.1442</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.441000000000001</v>
+        <v>-0.6036</v>
       </c>
       <c r="W17" t="n">
-        <v>7.690300000000001</v>
+        <v>-0.337</v>
       </c>
       <c r="X17" t="n">
-        <v>-12.1316</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TERNERO RODRIGUEZ</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5265</v>
+        <v>-0.1271999999999998</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7273</v>
+        <v>-5.808299999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2007</v>
+        <v>5.681100000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5803</v>
+        <v>4.3395</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8514</v>
+        <v>-3.431299999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7289</v>
+        <v>7.770799999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4142</v>
+        <v>14.74</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3701</v>
+        <v>4.119899999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0441</v>
+        <v>10.6202</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1661</v>
+        <v>-10.4008</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4813000000000001</v>
+        <v>-7.5515</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6849</v>
+        <v>-2.8492</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5947</v>
+        <v>3.9646</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1804</v>
+        <v>-30.1296</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>34.0944</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9086000000000001</v>
+        <v>-2.1894</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.624</v>
+        <v>0.09519999999999984</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2846</v>
+        <v>-2.2849</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6036</v>
+        <v>-6.2416</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.337</v>
+        <v>9.486000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2666</v>
+        <v>-15.7276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.706400000000002</v>
+        <v>-1.5876</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.8872</v>
+        <v>-9.503400000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>11.1809</v>
+        <v>7.9156</v>
       </c>
       <c r="G19" t="n">
-        <v>-11.2358</v>
+        <v>4.950799999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.5544</v>
+        <v>-0.1162999999999994</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6815000000000004</v>
+        <v>5.066800000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.018</v>
+        <v>6.7363</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.390000000000001</v>
+        <v>3.0126</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3722</v>
+        <v>3.7237</v>
       </c>
       <c r="M19" t="n">
-        <v>-10.2179</v>
+        <v>-1.785500000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-7.1643</v>
+        <v>-3.1291</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.0533</v>
+        <v>1.3436</v>
       </c>
       <c r="P19" t="n">
-        <v>6.541399999999999</v>
+        <v>4.162699999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-25.7688</v>
+        <v>-24.5794</v>
       </c>
       <c r="R19" t="n">
-        <v>32.3106</v>
+        <v>28.7423</v>
       </c>
       <c r="S19" t="n">
-        <v>-13.3703</v>
+        <v>8.0246</v>
       </c>
       <c r="T19" t="n">
-        <v>-11.2055</v>
+        <v>6.1372</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1653</v>
+        <v>1.8873</v>
       </c>
       <c r="V19" t="n">
-        <v>13.3585</v>
+        <v>-18.7255</v>
       </c>
       <c r="W19" t="n">
-        <v>22.1053</v>
+        <v>2.2031</v>
       </c>
       <c r="X19" t="n">
-        <v>-8.7468</v>
+        <v>-20.9284</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>-11.9382</v>
+        <v>-7.534400000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-12.255</v>
+        <v>-9.254799999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3166</v>
+        <v>1.7205</v>
       </c>
       <c r="G20" t="n">
         <v>-5.88</v>
@@ -2014,13 +2014,13 @@
         <v>7.7307</v>
       </c>
       <c r="S20" t="n">
-        <v>-4.225</v>
+        <v>0.1789</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8388</v>
+        <v>1.1617</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.3867</v>
+        <v>-0.9825999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-4.0136</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>-16.6869</v>
+        <v>-8.609599999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.2973</v>
+        <v>-19.3144</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3899999999999995</v>
+        <v>10.7046</v>
       </c>
       <c r="G21" t="n">
-        <v>4.3395</v>
+        <v>-8.9451</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.431299999999999</v>
+        <v>3.5291</v>
       </c>
       <c r="I21" t="n">
-        <v>7.770799999999999</v>
+        <v>-12.4743</v>
       </c>
       <c r="J21" t="n">
-        <v>14.74</v>
+        <v>-5.6474</v>
       </c>
       <c r="K21" t="n">
-        <v>4.119899999999999</v>
+        <v>8.334199999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>10.6202</v>
+        <v>-13.9818</v>
       </c>
       <c r="M21" t="n">
-        <v>-10.4008</v>
+        <v>-3.2974</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.5515</v>
+        <v>-4.8052</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.8492</v>
+        <v>1.5075</v>
       </c>
       <c r="P21" t="n">
-        <v>3.9646</v>
+        <v>-1.3877</v>
       </c>
       <c r="Q21" t="n">
-        <v>-30.1296</v>
+        <v>-25.5703</v>
       </c>
       <c r="R21" t="n">
-        <v>34.0944</v>
+        <v>24.1832</v>
       </c>
       <c r="S21" t="n">
-        <v>-18.7491</v>
+        <v>6.1641</v>
       </c>
       <c r="T21" t="n">
-        <v>-10.3935</v>
+        <v>4.2136</v>
       </c>
       <c r="U21" t="n">
-        <v>-8.356</v>
+        <v>1.9504</v>
       </c>
       <c r="V21" t="n">
-        <v>-6.2416</v>
+        <v>-4.441000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>9.486000000000001</v>
+        <v>7.690300000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>-15.7276</v>
+        <v>-12.1316</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>223.7144</v>
+        <v>247.8600999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>98.78969999999998</v>
+        <v>106.5902</v>
       </c>
       <c r="F22" t="n">
-        <v>124.9234</v>
+        <v>141.2692</v>
       </c>
       <c r="G22" t="n">
         <v>120.6632</v>
@@ -2149,37 +2149,37 @@
         <v>150.9455</v>
       </c>
       <c r="L22" t="n">
-        <v>94.29780000000001</v>
+        <v>94.2978</v>
       </c>
       <c r="M22" t="n">
         <v>-124.5792</v>
       </c>
       <c r="N22" t="n">
-        <v>-85.48200000000001</v>
+        <v>-85.482</v>
       </c>
       <c r="O22" t="n">
         <v>-39.09570000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>59.46699999999998</v>
+        <v>59.46699999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-370.6742</v>
+        <v>-370.6741999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>430.1437000000001</v>
+        <v>430.1437</v>
       </c>
       <c r="S22" t="n">
-        <v>29.0735</v>
+        <v>53.2189</v>
       </c>
       <c r="T22" t="n">
-        <v>35.6583</v>
+        <v>43.4594</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.586000000000001</v>
+        <v>9.7597</v>
       </c>
       <c r="V22" t="n">
-        <v>14.50989999999999</v>
+        <v>14.5099</v>
       </c>
       <c r="W22" t="n">
         <v>188.5664</v>
